--- a/data.mn/public/datasets/mongolbank-exchange-rates-annual-average-major.xlsx
+++ b/data.mn/public/datasets/mongolbank-exchange-rates-annual-average-major.xlsx
@@ -416,6 +416,43 @@
   </sheetPr>
   <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -630,7 +667,7 @@
         <v>493.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>513.6900000000001</v>
+        <v>522.98</v>
       </c>
     </row>
     <row r="3">
@@ -727,7 +764,7 @@
         <v>4008.82</v>
       </c>
       <c r="AI3" t="n">
-        <v>4200.32</v>
+        <v>4157.14</v>
       </c>
     </row>
     <row r="4">
@@ -836,7 +873,7 @@
         <v>23.72</v>
       </c>
       <c r="AI4" t="n">
-        <v>22.84</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="5">
@@ -943,7 +980,7 @@
         <v>42.66</v>
       </c>
       <c r="AI5" t="n">
-        <v>45.98</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="6">
@@ -1046,7 +1083,7 @@
         <v>2.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="7">
@@ -1155,7 +1192,7 @@
         <v>3545.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>3563.45</v>
+        <v>3575.12</v>
       </c>
     </row>
   </sheetData>
@@ -1171,6 +1208,43 @@
   </sheetPr>
   <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1387,7 +1461,7 @@
         <v>3545.14</v>
       </c>
       <c r="AI2" t="n">
-        <v>3563.45</v>
+        <v>3575.12</v>
       </c>
     </row>
     <row r="3">
@@ -1490,7 +1564,7 @@
         <v>2.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="4">
@@ -1587,7 +1661,7 @@
         <v>4008.82</v>
       </c>
       <c r="AI4" t="n">
-        <v>4200.32</v>
+        <v>4157.14</v>
       </c>
     </row>
     <row r="5">
@@ -1694,7 +1768,7 @@
         <v>42.66</v>
       </c>
       <c r="AI5" t="n">
-        <v>45.98</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="6">
@@ -1801,7 +1875,7 @@
         <v>493.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>513.6900000000001</v>
+        <v>522.98</v>
       </c>
     </row>
     <row r="7">
@@ -1910,7 +1984,7 @@
         <v>23.72</v>
       </c>
       <c r="AI7" t="n">
-        <v>22.84</v>
+        <v>22.52</v>
       </c>
     </row>
   </sheetData>
